--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130290522</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130290577</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130290522</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130290577</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130290522</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130290577</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130290522</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130290577</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130290522</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130290577</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130290522</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130290577</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>131137098</v>
       </c>
       <c r="B8" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>131137298</v>
       </c>
       <c r="B4" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131137846</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131137572</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>131137857</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131137098</v>
       </c>
       <c r="B8" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>131137298</v>
       </c>
       <c r="B4" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131137846</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131137572</v>
       </c>
       <c r="B6" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>131137857</v>
       </c>
       <c r="B7" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131137098</v>
       </c>
       <c r="B8" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>131137846</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131137572</v>
       </c>
       <c r="B6" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>131137857</v>
       </c>
       <c r="B7" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131137098</v>
       </c>
       <c r="B8" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>131137298</v>
       </c>
       <c r="B4" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131137846</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131137572</v>
       </c>
       <c r="B6" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>131137857</v>
       </c>
       <c r="B7" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131137098</v>
       </c>
       <c r="B8" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>131137298</v>
       </c>
       <c r="B4" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131137846</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131137572</v>
       </c>
       <c r="B6" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>131137857</v>
       </c>
       <c r="B7" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131137098</v>
       </c>
       <c r="B8" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>131137298</v>
       </c>
       <c r="B4" t="n">
-        <v>57071</v>
+        <v>57077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131137846</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131137572</v>
       </c>
       <c r="B6" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>131137857</v>
       </c>
       <c r="B7" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131137098</v>
       </c>
       <c r="B8" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1472,6 +1472,108 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131894750</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57082</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnfallet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480254</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6674263</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -1477,7 +1477,7 @@
         <v>131894750</v>
       </c>
       <c r="B9" t="n">
-        <v>57082</v>
+        <v>57083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -1477,7 +1477,7 @@
         <v>131894750</v>
       </c>
       <c r="B9" t="n">
-        <v>57083</v>
+        <v>57086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -1477,7 +1477,7 @@
         <v>131894750</v>
       </c>
       <c r="B9" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -1477,7 +1477,7 @@
         <v>131894750</v>
       </c>
       <c r="B9" t="n">
-        <v>57091</v>
+        <v>57093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -1477,7 +1477,7 @@
         <v>131894750</v>
       </c>
       <c r="B9" t="n">
-        <v>57093</v>
+        <v>57127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47287-2025 artfynd.xlsx
+++ b/artfynd/A 47287-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>130290522</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -785,11 +785,11 @@
         <v>130290577</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131137298</v>
+        <v>131137098</v>
       </c>
       <c r="B4" t="n">
-        <v>57077</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480012</v>
+        <v>479869</v>
       </c>
       <c r="R4" t="n">
-        <v>6674519</v>
+        <v>6674500</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 par födosökande</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,6 +980,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,7 +1014,7 @@
         <v>131137846</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,50 +1133,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131137572</v>
+        <v>131137298</v>
       </c>
       <c r="B6" t="n">
-        <v>58057</v>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnfallet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480040</v>
+        <v>480012</v>
       </c>
       <c r="R6" t="n">
-        <v>6674318</v>
+        <v>6674519</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 st</t>
+          <t>1 par födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,38 +1245,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131137857</v>
+        <v>131894750</v>
       </c>
       <c r="B7" t="n">
-        <v>58057</v>
+        <v>57153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480066</v>
+        <v>480254</v>
       </c>
       <c r="R7" t="n">
-        <v>6674279</v>
+        <v>6674263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,22 +1315,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131137098</v>
+        <v>131137572</v>
       </c>
       <c r="B8" t="n">
-        <v>80365</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,34 +1358,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarnfallet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479869</v>
+        <v>480040</v>
       </c>
       <c r="R8" t="n">
-        <v>6674500</v>
+        <v>6674318</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,21 +1448,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1474,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131894750</v>
+        <v>131137857</v>
       </c>
       <c r="B9" t="n">
-        <v>57128</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,27 +1475,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1514,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480254</v>
+        <v>480066</v>
       </c>
       <c r="R9" t="n">
-        <v>6674263</v>
+        <v>6674279</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1534,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
